--- a/artfynd/A 39815-2023 artfynd.xlsx
+++ b/artfynd/A 39815-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39815-2023 artfynd.xlsx
+++ b/artfynd/A 39815-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,440 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118106841</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80439</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ö Långremsbäcken, SÖ nyckelbiotopen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>608527</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6950482</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>kelohögstubbe</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118106754</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79071</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ö Långremsbäcken, Ö nyckelbiotopen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608442</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6950503</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118106791</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79100</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ö Långremsbäcken, SÖ nyckelbiotopen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>608473</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6950521</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>tallstubbe</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118106809</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ö Långremsbäcken, SÖ nyckelbiotopen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>608505</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6950512</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Måns Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Måns Svensson, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39815-2023 artfynd.xlsx
+++ b/artfynd/A 39815-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17270969</v>
+        <v>118106841</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Glupen, Mpd</t>
+          <t>Ö Långremsbäcken, SÖ nyckelbiotopen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608490.0929679356</v>
+        <v>608527</v>
       </c>
       <c r="R2" t="n">
-        <v>6950541.981108929</v>
+        <v>6950482</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-07-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>kelohögstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,46 +762,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Måns Svensson, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17268393</v>
+        <v>118106809</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -833,24 +809,23 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Glupen, Mpd</t>
+          <t>Ö Långremsbäcken, SÖ nyckelbiotopen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608490.0929679356</v>
+        <v>608505</v>
       </c>
       <c r="R3" t="n">
-        <v>6950541.981108929</v>
+        <v>6950512</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-07-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-07-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,42 +863,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Måns Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Måns Svensson, Alexander Hoffmann</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>118106791</v>
       </c>
       <c r="B4" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,12 +991,7 @@
         <v>118106754</v>
       </c>
       <c r="B5" t="n">
-        <v>79073</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,223 +1087,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>118106841</v>
-      </c>
-      <c r="B6" t="n">
-        <v>80441</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Microcalicium ahlneri</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Ö Långremsbäcken, SÖ nyckelbiotopen, Mpd</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>608527</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6950482</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Timrå</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Ljustorp</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>kelohögstubbe</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Måns Svensson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Måns Svensson, Alexander Hoffmann</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>118106809</v>
-      </c>
-      <c r="B7" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ö Långremsbäcken, SÖ nyckelbiotopen, Mpd</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>608505</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6950512</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Timrå</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Ljustorp</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-06-27</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Måns Svensson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Måns Svensson, Alexander Hoffmann</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39815-2023 artfynd.xlsx
+++ b/artfynd/A 39815-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118106841</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118106809</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118106791</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,8 +1106,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118106754</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>